--- a/AC_2009/AC_029.xlsx
+++ b/AC_2009/AC_029.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -45,8 +45,14 @@
     <font>
       <b val="1"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -59,8 +65,26 @@
         <bgColor rgb="001F497D"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+        <bgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9E1F2"/>
+        <bgColor rgb="00D9E1F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2EFDA"/>
+        <bgColor rgb="00E2EFDA"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -82,11 +106,53 @@
         <color rgb="00D9D9D9"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D3D3D3"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D3D3D3"/>
+      </right>
+      <top style="medium">
+        <color rgb="001B365D"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D3D3D3"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D3D3D3"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D3D3D3"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D3D3D3"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D3D3D3"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D3D3D3"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D3D3D3"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D3D3D3"/>
+      </top>
+      <bottom style="double">
+        <color rgb="001B365D"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -102,6 +168,18 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="5" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="5" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="5" fillId="5" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -468,7 +546,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W229"/>
+  <dimension ref="A1:W231"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -513,6 +591,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
@@ -521,7 +600,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Candidate_1</t>
+          <t>PS_Name</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -16911,93 +16990,257 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="6" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B229" s="7">
-        <f>SUM(B6:B228)</f>
-        <v/>
-      </c>
-      <c r="C229" s="7">
+      <c r="A229" s="8" t="inlineStr">
+        <is>
+          <t>TOTAL EVM VOTES</t>
+        </is>
+      </c>
+      <c r="B229" s="9" t="inlineStr"/>
+      <c r="C229" s="9">
         <f>SUM(C6:C228)</f>
         <v/>
       </c>
-      <c r="D229" s="7">
+      <c r="D229" s="9">
         <f>SUM(D6:D228)</f>
         <v/>
       </c>
-      <c r="E229" s="7">
+      <c r="E229" s="9">
         <f>SUM(E6:E228)</f>
         <v/>
       </c>
-      <c r="F229" s="7">
+      <c r="F229" s="9">
         <f>SUM(F6:F228)</f>
         <v/>
       </c>
-      <c r="G229" s="7">
+      <c r="G229" s="9">
         <f>SUM(G6:G228)</f>
         <v/>
       </c>
-      <c r="H229" s="7">
+      <c r="H229" s="9">
         <f>SUM(H6:H228)</f>
         <v/>
       </c>
-      <c r="I229" s="7">
+      <c r="I229" s="9">
         <f>SUM(I6:I228)</f>
         <v/>
       </c>
-      <c r="J229" s="7">
+      <c r="J229" s="9">
         <f>SUM(J6:J228)</f>
         <v/>
       </c>
-      <c r="K229" s="7">
+      <c r="K229" s="9">
         <f>SUM(K6:K228)</f>
         <v/>
       </c>
-      <c r="L229" s="7">
+      <c r="L229" s="9">
         <f>SUM(L6:L228)</f>
         <v/>
       </c>
-      <c r="M229" s="7">
+      <c r="M229" s="9">
         <f>SUM(M6:M228)</f>
         <v/>
       </c>
-      <c r="N229" s="7">
+      <c r="N229" s="9">
         <f>SUM(N6:N228)</f>
         <v/>
       </c>
-      <c r="O229" s="7">
+      <c r="O229" s="9">
         <f>SUM(O6:O228)</f>
         <v/>
       </c>
-      <c r="P229" s="7">
+      <c r="P229" s="9">
         <f>SUM(P6:P228)</f>
         <v/>
       </c>
-      <c r="Q229" s="7">
+      <c r="Q229" s="9">
         <f>SUM(Q6:Q228)</f>
         <v/>
       </c>
-      <c r="R229" s="7">
+      <c r="R229" s="9">
         <f>SUM(R6:R228)</f>
         <v/>
       </c>
-      <c r="S229" s="7">
+      <c r="S229" s="9">
         <f>SUM(S6:S228)</f>
         <v/>
       </c>
-      <c r="T229" s="7">
+      <c r="T229" s="9">
         <f>SUM(T6:T228)</f>
         <v/>
       </c>
-      <c r="U229" s="7">
+      <c r="U229" s="9">
         <f>SUM(U6:U228)</f>
         <v/>
       </c>
-      <c r="V229" s="7">
+      <c r="V229" s="9">
         <f>SUM(V6:V228)</f>
+        <v/>
+      </c>
+      <c r="W229" s="9">
+        <f>SUM(W6:W228)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="10" t="inlineStr">
+        <is>
+          <t>POSTAL BALLOT VOTES</t>
+        </is>
+      </c>
+      <c r="B230" s="11" t="inlineStr"/>
+      <c r="C230" s="11" t="n">
+        <v>15</v>
+      </c>
+      <c r="D230" s="11" t="n">
+        <v>224</v>
+      </c>
+      <c r="E230" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="F230" s="11" t="n">
+        <v>30</v>
+      </c>
+      <c r="G230" s="11" t="n">
+        <v>42</v>
+      </c>
+      <c r="H230" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I230" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J230" s="11" t="n">
+        <v>11</v>
+      </c>
+      <c r="K230" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L230" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M230" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N230" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O230" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P230" s="11" t="n">
+        <v>323</v>
+      </c>
+      <c r="Q230" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R230" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S230" s="11" t="n">
+        <v>653</v>
+      </c>
+      <c r="T230" s="11" t="n">
+        <v>28</v>
+      </c>
+      <c r="U230" s="11" t="n">
+        <v>681</v>
+      </c>
+      <c r="V230" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="W230" s="11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="12" t="inlineStr">
+        <is>
+          <t>TOTAL VOTES POLLED</t>
+        </is>
+      </c>
+      <c r="B231" s="13" t="inlineStr"/>
+      <c r="C231" s="13">
+        <f>C229+C230</f>
+        <v/>
+      </c>
+      <c r="D231" s="13">
+        <f>D229+D230</f>
+        <v/>
+      </c>
+      <c r="E231" s="13">
+        <f>E229+E230</f>
+        <v/>
+      </c>
+      <c r="F231" s="13">
+        <f>F229+F230</f>
+        <v/>
+      </c>
+      <c r="G231" s="13">
+        <f>G229+G230</f>
+        <v/>
+      </c>
+      <c r="H231" s="13">
+        <f>H229+H230</f>
+        <v/>
+      </c>
+      <c r="I231" s="13">
+        <f>I229+I230</f>
+        <v/>
+      </c>
+      <c r="J231" s="13">
+        <f>J229+J230</f>
+        <v/>
+      </c>
+      <c r="K231" s="13">
+        <f>K229+K230</f>
+        <v/>
+      </c>
+      <c r="L231" s="13">
+        <f>L229+L230</f>
+        <v/>
+      </c>
+      <c r="M231" s="13">
+        <f>M229+M230</f>
+        <v/>
+      </c>
+      <c r="N231" s="13">
+        <f>N229+N230</f>
+        <v/>
+      </c>
+      <c r="O231" s="13">
+        <f>O229+O230</f>
+        <v/>
+      </c>
+      <c r="P231" s="13">
+        <f>P229+P230</f>
+        <v/>
+      </c>
+      <c r="Q231" s="13">
+        <f>Q229+Q230</f>
+        <v/>
+      </c>
+      <c r="R231" s="13">
+        <f>R229+R230</f>
+        <v/>
+      </c>
+      <c r="S231" s="13">
+        <f>S229+S230</f>
+        <v/>
+      </c>
+      <c r="T231" s="13">
+        <f>T229+T230</f>
+        <v/>
+      </c>
+      <c r="U231" s="13">
+        <f>U229+U230</f>
+        <v/>
+      </c>
+      <c r="V231" s="13">
+        <f>V229+V230</f>
+        <v/>
+      </c>
+      <c r="W231" s="13">
+        <f>W229+W230</f>
         <v/>
       </c>
     </row>

--- a/AC_2009/AC_029.xlsx
+++ b/AC_2009/AC_029.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -50,6 +50,11 @@
       <b val="1"/>
       <color rgb="00000000"/>
       <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="6">
@@ -84,7 +89,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -148,11 +153,19 @@
         <color rgb="001B365D"/>
       </bottom>
     </border>
+    <border>
+      <top style="thin">
+        <color rgb="00D9D9D9"/>
+      </top>
+      <bottom style="double">
+        <color rgb="00000000"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -179,6 +192,27 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="5" fillId="5" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="3" fontId="5" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="3" fontId="5" fillId="4" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="4" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
@@ -591,7 +625,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
@@ -16990,256 +17023,256 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="8" t="inlineStr">
+      <c r="A229" s="14" t="inlineStr">
         <is>
           <t>TOTAL EVM VOTES</t>
         </is>
       </c>
-      <c r="B229" s="9" t="inlineStr"/>
-      <c r="C229" s="9">
+      <c r="B229" s="15" t="inlineStr"/>
+      <c r="C229" s="16">
         <f>SUM(C6:C228)</f>
         <v/>
       </c>
-      <c r="D229" s="9">
+      <c r="D229" s="16">
         <f>SUM(D6:D228)</f>
         <v/>
       </c>
-      <c r="E229" s="9">
+      <c r="E229" s="16">
         <f>SUM(E6:E228)</f>
         <v/>
       </c>
-      <c r="F229" s="9">
+      <c r="F229" s="16">
         <f>SUM(F6:F228)</f>
         <v/>
       </c>
-      <c r="G229" s="9">
+      <c r="G229" s="16">
         <f>SUM(G6:G228)</f>
         <v/>
       </c>
-      <c r="H229" s="9">
+      <c r="H229" s="16">
         <f>SUM(H6:H228)</f>
         <v/>
       </c>
-      <c r="I229" s="9">
+      <c r="I229" s="16">
         <f>SUM(I6:I228)</f>
         <v/>
       </c>
-      <c r="J229" s="9">
+      <c r="J229" s="16">
         <f>SUM(J6:J228)</f>
         <v/>
       </c>
-      <c r="K229" s="9">
+      <c r="K229" s="16">
         <f>SUM(K6:K228)</f>
         <v/>
       </c>
-      <c r="L229" s="9">
+      <c r="L229" s="16">
         <f>SUM(L6:L228)</f>
         <v/>
       </c>
-      <c r="M229" s="9">
+      <c r="M229" s="16">
         <f>SUM(M6:M228)</f>
         <v/>
       </c>
-      <c r="N229" s="9">
+      <c r="N229" s="16">
         <f>SUM(N6:N228)</f>
         <v/>
       </c>
-      <c r="O229" s="9">
+      <c r="O229" s="16">
         <f>SUM(O6:O228)</f>
         <v/>
       </c>
-      <c r="P229" s="9">
+      <c r="P229" s="16">
         <f>SUM(P6:P228)</f>
         <v/>
       </c>
-      <c r="Q229" s="9">
+      <c r="Q229" s="16">
         <f>SUM(Q6:Q228)</f>
         <v/>
       </c>
-      <c r="R229" s="9">
+      <c r="R229" s="16">
         <f>SUM(R6:R228)</f>
         <v/>
       </c>
-      <c r="S229" s="9">
+      <c r="S229" s="16">
         <f>SUM(S6:S228)</f>
         <v/>
       </c>
-      <c r="T229" s="9">
+      <c r="T229" s="16">
         <f>SUM(T6:T228)</f>
         <v/>
       </c>
-      <c r="U229" s="9">
+      <c r="U229" s="16">
         <f>SUM(U6:U228)</f>
         <v/>
       </c>
-      <c r="V229" s="9">
+      <c r="V229" s="16">
         <f>SUM(V6:V228)</f>
         <v/>
       </c>
-      <c r="W229" s="9">
+      <c r="W229" s="16">
         <f>SUM(W6:W228)</f>
         <v/>
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="10" t="inlineStr">
+      <c r="A230" s="17" t="inlineStr">
         <is>
           <t>POSTAL BALLOT VOTES</t>
         </is>
       </c>
       <c r="B230" s="11" t="inlineStr"/>
-      <c r="C230" s="11" t="n">
+      <c r="C230" s="16" t="n">
         <v>15</v>
       </c>
-      <c r="D230" s="11" t="n">
+      <c r="D230" s="16" t="n">
         <v>224</v>
       </c>
-      <c r="E230" s="11" t="n">
+      <c r="E230" s="16" t="n">
         <v>8</v>
       </c>
-      <c r="F230" s="11" t="n">
+      <c r="F230" s="16" t="n">
         <v>30</v>
       </c>
-      <c r="G230" s="11" t="n">
+      <c r="G230" s="16" t="n">
         <v>42</v>
       </c>
-      <c r="H230" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I230" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J230" s="11" t="n">
+      <c r="H230" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I230" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J230" s="16" t="n">
         <v>11</v>
       </c>
-      <c r="K230" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L230" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M230" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N230" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O230" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P230" s="11" t="n">
+      <c r="K230" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L230" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M230" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N230" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O230" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P230" s="16" t="n">
         <v>323</v>
       </c>
-      <c r="Q230" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="R230" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S230" s="11" t="n">
+      <c r="Q230" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R230" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S230" s="16" t="n">
         <v>653</v>
       </c>
-      <c r="T230" s="11" t="n">
+      <c r="T230" s="16" t="n">
         <v>28</v>
       </c>
-      <c r="U230" s="11" t="n">
+      <c r="U230" s="16" t="n">
         <v>681</v>
       </c>
-      <c r="V230" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="W230" s="11" t="n">
+      <c r="V230" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W230" s="16" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="12" t="inlineStr">
+      <c r="A231" s="18" t="inlineStr">
         <is>
           <t>TOTAL VOTES POLLED</t>
         </is>
       </c>
-      <c r="B231" s="13" t="inlineStr"/>
-      <c r="C231" s="13">
+      <c r="B231" s="19" t="inlineStr"/>
+      <c r="C231" s="20">
         <f>C229+C230</f>
         <v/>
       </c>
-      <c r="D231" s="13">
+      <c r="D231" s="20">
         <f>D229+D230</f>
         <v/>
       </c>
-      <c r="E231" s="13">
+      <c r="E231" s="20">
         <f>E229+E230</f>
         <v/>
       </c>
-      <c r="F231" s="13">
+      <c r="F231" s="20">
         <f>F229+F230</f>
         <v/>
       </c>
-      <c r="G231" s="13">
+      <c r="G231" s="20">
         <f>G229+G230</f>
         <v/>
       </c>
-      <c r="H231" s="13">
+      <c r="H231" s="20">
         <f>H229+H230</f>
         <v/>
       </c>
-      <c r="I231" s="13">
+      <c r="I231" s="20">
         <f>I229+I230</f>
         <v/>
       </c>
-      <c r="J231" s="13">
+      <c r="J231" s="20">
         <f>J229+J230</f>
         <v/>
       </c>
-      <c r="K231" s="13">
+      <c r="K231" s="20">
         <f>K229+K230</f>
         <v/>
       </c>
-      <c r="L231" s="13">
+      <c r="L231" s="20">
         <f>L229+L230</f>
         <v/>
       </c>
-      <c r="M231" s="13">
+      <c r="M231" s="20">
         <f>M229+M230</f>
         <v/>
       </c>
-      <c r="N231" s="13">
+      <c r="N231" s="20">
         <f>N229+N230</f>
         <v/>
       </c>
-      <c r="O231" s="13">
+      <c r="O231" s="20">
         <f>O229+O230</f>
         <v/>
       </c>
-      <c r="P231" s="13">
+      <c r="P231" s="20">
         <f>P229+P230</f>
         <v/>
       </c>
-      <c r="Q231" s="13">
+      <c r="Q231" s="20">
         <f>Q229+Q230</f>
         <v/>
       </c>
-      <c r="R231" s="13">
+      <c r="R231" s="20">
         <f>R229+R230</f>
         <v/>
       </c>
-      <c r="S231" s="13">
+      <c r="S231" s="20">
         <f>S229+S230</f>
         <v/>
       </c>
-      <c r="T231" s="13">
+      <c r="T231" s="20">
         <f>T229+T230</f>
         <v/>
       </c>
-      <c r="U231" s="13">
+      <c r="U231" s="20">
         <f>U229+U230</f>
         <v/>
       </c>
-      <c r="V231" s="13">
+      <c r="V231" s="20">
         <f>V229+V230</f>
         <v/>
       </c>
-      <c r="W231" s="13">
+      <c r="W231" s="20">
         <f>W229+W230</f>
         <v/>
       </c>

--- a/AC_2009/AC_029.xlsx
+++ b/AC_2009/AC_029.xlsx
@@ -1465,7 +1465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W231"/>
+  <dimension ref="A1:V231"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.83333" defaultRowHeight="15" customHeight="1" outlineLevelRow="0"/>
   <cols>
     <col width="35" customWidth="1" style="1" min="1" max="1"/>
@@ -1488,8 +1488,7 @@
     <col width="17" customWidth="1" style="1" min="20" max="20"/>
     <col width="16" customWidth="1" style="1" min="21" max="21"/>
     <col width="17" customWidth="1" style="1" min="22" max="22"/>
-    <col width="16" customWidth="1" style="1" min="23" max="23"/>
-    <col width="8.851559999999999" customWidth="1" style="1" min="24" max="16384"/>
+    <col width="8.851559999999999" customWidth="1" style="1" min="23" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="15.35" customHeight="1" s="24">
@@ -1515,7 +1514,6 @@
       <c r="T1" s="3" t="n"/>
       <c r="U1" s="3" t="n"/>
       <c r="V1" s="3" t="n"/>
-      <c r="W1" s="3" t="n"/>
     </row>
     <row r="2" ht="13.75" customHeight="1" s="24">
       <c r="A2" s="4" t="inlineStr">
@@ -1544,7 +1542,6 @@
       <c r="T2" s="3" t="n"/>
       <c r="U2" s="3" t="n"/>
       <c r="V2" s="3" t="n"/>
-      <c r="W2" s="3" t="n"/>
     </row>
     <row r="3" ht="13.75" customHeight="1" s="24">
       <c r="A3" s="4" t="inlineStr">
@@ -1573,7 +1570,6 @@
       <c r="T3" s="3" t="n"/>
       <c r="U3" s="3" t="n"/>
       <c r="V3" s="3" t="n"/>
-      <c r="W3" s="3" t="n"/>
     </row>
     <row r="4" ht="13.55" customHeight="1" s="24">
       <c r="A4" s="5" t="n"/>
@@ -1598,7 +1594,6 @@
       <c r="T4" s="5" t="n"/>
       <c r="U4" s="5" t="n"/>
       <c r="V4" s="5" t="n"/>
-      <c r="W4" s="5" t="n"/>
     </row>
     <row r="5" ht="13.55" customHeight="1" s="24">
       <c r="A5" s="6" t="inlineStr">
@@ -1706,14 +1701,9 @@
           <t>Total_Votes</t>
         </is>
       </c>
-      <c r="V5" s="7" t="inlineStr">
+      <c r="V5" s="8" t="inlineStr">
         <is>
           <t>Tendered_Votes</t>
-        </is>
-      </c>
-      <c r="W5" s="8" t="inlineStr">
-        <is>
-          <t>Checksum_Diff</t>
         </is>
       </c>
     </row>
@@ -1786,9 +1776,6 @@
       <c r="V6" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W6" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="7" ht="13.55" customHeight="1" s="24">
       <c r="A7" s="9" t="n">
@@ -1859,9 +1846,6 @@
       <c r="V7" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W7" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="8" ht="13.55" customHeight="1" s="24">
       <c r="A8" s="9" t="n">
@@ -1932,9 +1916,6 @@
       <c r="V8" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W8" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="9" ht="13.55" customHeight="1" s="24">
       <c r="A9" s="9" t="n">
@@ -2005,9 +1986,6 @@
       <c r="V9" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W9" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="10" ht="13.55" customHeight="1" s="24">
       <c r="A10" s="9" t="n">
@@ -2076,9 +2054,6 @@
         <v>695</v>
       </c>
       <c r="V10" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W10" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2151,9 +2126,6 @@
       <c r="V11" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W11" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="12" ht="13.55" customHeight="1" s="24">
       <c r="A12" s="9" t="n">
@@ -2224,9 +2196,6 @@
       <c r="V12" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W12" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="13" ht="13.55" customHeight="1" s="24">
       <c r="A13" s="9" t="n">
@@ -2297,9 +2266,6 @@
       <c r="V13" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W13" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="14" ht="13.55" customHeight="1" s="24">
       <c r="A14" s="9" t="n">
@@ -2370,9 +2336,6 @@
       <c r="V14" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W14" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="15" ht="13.55" customHeight="1" s="24">
       <c r="A15" s="9" t="n">
@@ -2443,9 +2406,6 @@
       <c r="V15" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W15" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="16" ht="13.55" customHeight="1" s="24">
       <c r="A16" s="9" t="n">
@@ -2516,9 +2476,6 @@
       <c r="V16" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W16" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="17" ht="13.55" customHeight="1" s="24">
       <c r="A17" s="9" t="n">
@@ -2589,9 +2546,6 @@
       <c r="V17" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W17" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="18" ht="13.55" customHeight="1" s="24">
       <c r="A18" s="9" t="n">
@@ -2662,9 +2616,6 @@
       <c r="V18" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W18" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="19" ht="13.55" customHeight="1" s="24">
       <c r="A19" s="9" t="n">
@@ -2735,9 +2686,6 @@
       <c r="V19" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W19" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="20" ht="13.55" customHeight="1" s="24">
       <c r="A20" s="9" t="n">
@@ -2808,9 +2756,6 @@
       <c r="V20" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W20" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="21" ht="13.55" customHeight="1" s="24">
       <c r="A21" s="9" t="n">
@@ -2881,9 +2826,6 @@
       <c r="V21" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W21" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="22" ht="13.55" customHeight="1" s="24">
       <c r="A22" s="9" t="n">
@@ -2954,9 +2896,6 @@
       <c r="V22" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W22" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="23" ht="13.55" customHeight="1" s="24">
       <c r="A23" s="9" t="n">
@@ -3027,9 +2966,6 @@
       <c r="V23" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W23" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="24" ht="13.55" customHeight="1" s="24">
       <c r="A24" s="9" t="n">
@@ -3100,9 +3036,6 @@
       <c r="V24" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W24" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="25" ht="13.55" customHeight="1" s="24">
       <c r="A25" s="9" t="n">
@@ -3173,9 +3106,6 @@
       <c r="V25" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W25" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="26" ht="13.55" customHeight="1" s="24">
       <c r="A26" s="9" t="n">
@@ -3246,9 +3176,6 @@
       <c r="V26" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W26" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="27" ht="13.55" customHeight="1" s="24">
       <c r="A27" s="9" t="n">
@@ -3319,9 +3246,6 @@
       <c r="V27" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W27" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="28" ht="13.55" customHeight="1" s="24">
       <c r="A28" s="9" t="n">
@@ -3392,9 +3316,6 @@
       <c r="V28" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W28" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="29" ht="13.55" customHeight="1" s="24">
       <c r="A29" s="9" t="n">
@@ -3465,9 +3386,6 @@
       <c r="V29" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W29" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="30" ht="13.55" customHeight="1" s="24">
       <c r="A30" s="9" t="n">
@@ -3538,9 +3456,6 @@
       <c r="V30" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W30" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="31" ht="13.55" customHeight="1" s="24">
       <c r="A31" s="9" t="n">
@@ -3611,9 +3526,6 @@
       <c r="V31" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W31" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="32" ht="13.55" customHeight="1" s="24">
       <c r="A32" s="9" t="n">
@@ -3684,9 +3596,6 @@
       <c r="V32" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W32" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="33" ht="13.55" customHeight="1" s="24">
       <c r="A33" s="9" t="n">
@@ -3757,9 +3666,6 @@
       <c r="V33" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W33" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="34" ht="13.55" customHeight="1" s="24">
       <c r="A34" s="9" t="n">
@@ -3830,9 +3736,6 @@
       <c r="V34" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W34" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="35" ht="13.55" customHeight="1" s="24">
       <c r="A35" s="9" t="n">
@@ -3903,9 +3806,6 @@
       <c r="V35" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W35" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="36" ht="13.55" customHeight="1" s="24">
       <c r="A36" s="9" t="n">
@@ -3976,9 +3876,6 @@
       <c r="V36" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W36" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="37" ht="13.55" customHeight="1" s="24">
       <c r="A37" s="9" t="n">
@@ -4049,9 +3946,6 @@
       <c r="V37" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W37" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="38" ht="13.55" customHeight="1" s="24">
       <c r="A38" s="9" t="n">
@@ -4122,9 +4016,6 @@
       <c r="V38" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W38" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="39" ht="13.55" customHeight="1" s="24">
       <c r="A39" s="9" t="n">
@@ -4195,9 +4086,6 @@
       <c r="V39" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W39" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="40" ht="13.55" customHeight="1" s="24">
       <c r="A40" s="9" t="n">
@@ -4268,9 +4156,6 @@
       <c r="V40" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W40" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="41" ht="13.55" customHeight="1" s="24">
       <c r="A41" s="9" t="n">
@@ -4341,9 +4226,6 @@
       <c r="V41" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W41" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="42" ht="13.55" customHeight="1" s="24">
       <c r="A42" s="9" t="n">
@@ -4414,9 +4296,6 @@
       <c r="V42" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W42" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="43" ht="13.55" customHeight="1" s="24">
       <c r="A43" s="9" t="n">
@@ -4487,9 +4366,6 @@
       <c r="V43" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W43" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="44" ht="13.55" customHeight="1" s="24">
       <c r="A44" s="9" t="n">
@@ -4560,9 +4436,6 @@
       <c r="V44" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W44" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="45" ht="13.55" customHeight="1" s="24">
       <c r="A45" s="9" t="n">
@@ -4633,9 +4506,6 @@
       <c r="V45" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W45" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="46" ht="13.55" customHeight="1" s="24">
       <c r="A46" s="9" t="n">
@@ -4706,9 +4576,6 @@
       <c r="V46" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W46" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="47" ht="13.55" customHeight="1" s="24">
       <c r="A47" s="9" t="n">
@@ -4779,9 +4646,6 @@
       <c r="V47" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W47" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="48" ht="13.55" customHeight="1" s="24">
       <c r="A48" s="9" t="n">
@@ -4852,9 +4716,6 @@
       <c r="V48" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W48" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="49" ht="13.55" customHeight="1" s="24">
       <c r="A49" s="9" t="n">
@@ -4925,9 +4786,6 @@
       <c r="V49" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W49" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="50" ht="13.55" customHeight="1" s="24">
       <c r="A50" s="9" t="n">
@@ -4998,9 +4856,6 @@
       <c r="V50" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W50" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="51" ht="13.55" customHeight="1" s="24">
       <c r="A51" s="9" t="n">
@@ -5071,9 +4926,6 @@
       <c r="V51" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W51" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="52" ht="13.55" customHeight="1" s="24">
       <c r="A52" s="9" t="n">
@@ -5144,9 +4996,6 @@
       <c r="V52" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W52" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="53" ht="13.55" customHeight="1" s="24">
       <c r="A53" s="9" t="n">
@@ -5217,9 +5066,6 @@
       <c r="V53" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W53" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="54" ht="13.55" customHeight="1" s="24">
       <c r="A54" s="9" t="n">
@@ -5290,9 +5136,6 @@
       <c r="V54" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W54" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="55" ht="13.55" customHeight="1" s="24">
       <c r="A55" s="9" t="n">
@@ -5363,9 +5206,6 @@
       <c r="V55" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W55" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="56" ht="13.55" customHeight="1" s="24">
       <c r="A56" s="9" t="n">
@@ -5436,9 +5276,6 @@
       <c r="V56" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W56" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="57" ht="13.55" customHeight="1" s="24">
       <c r="A57" s="9" t="n">
@@ -5509,9 +5346,6 @@
       <c r="V57" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W57" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="58" ht="13.55" customHeight="1" s="24">
       <c r="A58" s="9" t="n">
@@ -5582,9 +5416,6 @@
       <c r="V58" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W58" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="59" ht="13.55" customHeight="1" s="24">
       <c r="A59" s="9" t="n">
@@ -5655,9 +5486,6 @@
       <c r="V59" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W59" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="60" ht="13.55" customHeight="1" s="24">
       <c r="A60" s="9" t="n">
@@ -5728,9 +5556,6 @@
       <c r="V60" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W60" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="61" ht="13.55" customHeight="1" s="24">
       <c r="A61" s="9" t="n">
@@ -5801,9 +5626,6 @@
       <c r="V61" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W61" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="62" ht="13.55" customHeight="1" s="24">
       <c r="A62" s="9" t="n">
@@ -5874,9 +5696,6 @@
       <c r="V62" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W62" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="63" ht="13.55" customHeight="1" s="24">
       <c r="A63" s="9" t="n">
@@ -5947,9 +5766,6 @@
       <c r="V63" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W63" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="64" ht="13.55" customHeight="1" s="24">
       <c r="A64" s="9" t="n">
@@ -6020,9 +5836,6 @@
       <c r="V64" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W64" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="65" ht="13.55" customHeight="1" s="24">
       <c r="A65" s="9" t="n">
@@ -6093,9 +5906,6 @@
       <c r="V65" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W65" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="66" ht="13.55" customHeight="1" s="24">
       <c r="A66" s="9" t="n">
@@ -6166,9 +5976,6 @@
       <c r="V66" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W66" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="67" ht="13.55" customHeight="1" s="24">
       <c r="A67" s="9" t="n">
@@ -6239,9 +6046,6 @@
       <c r="V67" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W67" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="68" ht="13.55" customHeight="1" s="24">
       <c r="A68" s="9" t="n">
@@ -6312,9 +6116,6 @@
       <c r="V68" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W68" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="69" ht="13.55" customHeight="1" s="24">
       <c r="A69" s="9" t="n">
@@ -6385,9 +6186,6 @@
       <c r="V69" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W69" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="70" ht="13.55" customHeight="1" s="24">
       <c r="A70" s="9" t="n">
@@ -6458,9 +6256,6 @@
       <c r="V70" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W70" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="71" ht="13.55" customHeight="1" s="24">
       <c r="A71" s="9" t="n">
@@ -6531,9 +6326,6 @@
       <c r="V71" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W71" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="72" ht="13.55" customHeight="1" s="24">
       <c r="A72" s="9" t="n">
@@ -6604,9 +6396,6 @@
       <c r="V72" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W72" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="73" ht="13.55" customHeight="1" s="24">
       <c r="A73" s="9" t="n">
@@ -6677,9 +6466,6 @@
       <c r="V73" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W73" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="74" ht="13.55" customHeight="1" s="24">
       <c r="A74" s="9" t="n">
@@ -6750,9 +6536,6 @@
       <c r="V74" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W74" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="75" ht="13.55" customHeight="1" s="24">
       <c r="A75" s="9" t="n">
@@ -6823,9 +6606,6 @@
       <c r="V75" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W75" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="76" ht="13.55" customHeight="1" s="24">
       <c r="A76" s="9" t="n">
@@ -6896,9 +6676,6 @@
       <c r="V76" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W76" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="77" ht="13.55" customHeight="1" s="24">
       <c r="A77" s="9" t="n">
@@ -6969,9 +6746,6 @@
       <c r="V77" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W77" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="78" ht="13.55" customHeight="1" s="24">
       <c r="A78" s="9" t="n">
@@ -7042,9 +6816,6 @@
       <c r="V78" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W78" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="79" ht="13.55" customHeight="1" s="24">
       <c r="A79" s="9" t="n">
@@ -7115,9 +6886,6 @@
       <c r="V79" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W79" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="80" ht="13.55" customHeight="1" s="24">
       <c r="A80" s="9" t="n">
@@ -7188,9 +6956,6 @@
       <c r="V80" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W80" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="81" ht="13.55" customHeight="1" s="24">
       <c r="A81" s="9" t="n">
@@ -7261,9 +7026,6 @@
       <c r="V81" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W81" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="82" ht="13.55" customHeight="1" s="24">
       <c r="A82" s="9" t="n">
@@ -7334,9 +7096,6 @@
       <c r="V82" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W82" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="83" ht="13.55" customHeight="1" s="24">
       <c r="A83" s="9" t="n">
@@ -7407,9 +7166,6 @@
       <c r="V83" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W83" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="84" ht="13.55" customHeight="1" s="24">
       <c r="A84" s="9" t="n">
@@ -7480,9 +7236,6 @@
       <c r="V84" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W84" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="85" ht="13.55" customHeight="1" s="24">
       <c r="A85" s="9" t="n">
@@ -7553,9 +7306,6 @@
       <c r="V85" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W85" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="86" ht="13.55" customHeight="1" s="24">
       <c r="A86" s="9" t="n">
@@ -7626,9 +7376,6 @@
       <c r="V86" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W86" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="87" ht="13.55" customHeight="1" s="24">
       <c r="A87" s="9" t="n">
@@ -7699,9 +7446,6 @@
       <c r="V87" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W87" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="88" ht="13.55" customHeight="1" s="24">
       <c r="A88" s="9" t="n">
@@ -7772,9 +7516,6 @@
       <c r="V88" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W88" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="89" ht="13.55" customHeight="1" s="24">
       <c r="A89" s="9" t="n">
@@ -7845,9 +7586,6 @@
       <c r="V89" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W89" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="90" ht="13.55" customHeight="1" s="24">
       <c r="A90" s="9" t="n">
@@ -7918,9 +7656,6 @@
       <c r="V90" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W90" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="91" ht="13.55" customHeight="1" s="24">
       <c r="A91" s="9" t="n">
@@ -7991,9 +7726,6 @@
       <c r="V91" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W91" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="92" ht="13.55" customHeight="1" s="24">
       <c r="A92" s="9" t="n">
@@ -8064,9 +7796,6 @@
       <c r="V92" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W92" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="93" ht="13.55" customHeight="1" s="24">
       <c r="A93" s="9" t="n">
@@ -8137,9 +7866,6 @@
       <c r="V93" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W93" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="94" ht="13.55" customHeight="1" s="24">
       <c r="A94" s="9" t="n">
@@ -8210,9 +7936,6 @@
       <c r="V94" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W94" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="95" ht="13.55" customHeight="1" s="24">
       <c r="A95" s="9" t="n">
@@ -8283,9 +8006,6 @@
       <c r="V95" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W95" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="96" ht="13.55" customHeight="1" s="24">
       <c r="A96" s="9" t="n">
@@ -8356,9 +8076,6 @@
       <c r="V96" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W96" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="97" ht="13.55" customHeight="1" s="24">
       <c r="A97" s="9" t="n">
@@ -8429,9 +8146,6 @@
       <c r="V97" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W97" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="98" ht="13.55" customHeight="1" s="24">
       <c r="A98" s="9" t="n">
@@ -8502,9 +8216,6 @@
       <c r="V98" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W98" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="99" ht="13.55" customHeight="1" s="24">
       <c r="A99" s="9" t="n">
@@ -8575,9 +8286,6 @@
       <c r="V99" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W99" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="100" ht="13.55" customHeight="1" s="24">
       <c r="A100" s="9" t="n">
@@ -8648,9 +8356,6 @@
       <c r="V100" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W100" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="101" ht="13.55" customHeight="1" s="24">
       <c r="A101" s="9" t="n">
@@ -8721,9 +8426,6 @@
       <c r="V101" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W101" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="102" ht="13.55" customHeight="1" s="24">
       <c r="A102" s="9" t="n">
@@ -8794,9 +8496,6 @@
       <c r="V102" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W102" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="103" ht="13.55" customHeight="1" s="24">
       <c r="A103" s="9" t="n">
@@ -8867,9 +8566,6 @@
       <c r="V103" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W103" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="104" ht="13.55" customHeight="1" s="24">
       <c r="A104" s="9" t="n">
@@ -8940,9 +8636,6 @@
       <c r="V104" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W104" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="105" ht="13.55" customHeight="1" s="24">
       <c r="A105" s="9" t="n">
@@ -9013,9 +8706,6 @@
       <c r="V105" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W105" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="106" ht="13.55" customHeight="1" s="24">
       <c r="A106" s="9" t="n">
@@ -9086,9 +8776,6 @@
       <c r="V106" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W106" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="107" ht="13.55" customHeight="1" s="24">
       <c r="A107" s="9" t="n">
@@ -9159,9 +8846,6 @@
       <c r="V107" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W107" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="108" ht="13.55" customHeight="1" s="24">
       <c r="A108" s="9" t="n">
@@ -9232,9 +8916,6 @@
       <c r="V108" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W108" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="109" ht="13.55" customHeight="1" s="24">
       <c r="A109" s="9" t="n">
@@ -9305,9 +8986,6 @@
       <c r="V109" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W109" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="110" ht="13.55" customHeight="1" s="24">
       <c r="A110" s="9" t="n">
@@ -9378,9 +9056,6 @@
       <c r="V110" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W110" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="111" ht="13.55" customHeight="1" s="24">
       <c r="A111" s="9" t="n">
@@ -9451,9 +9126,6 @@
       <c r="V111" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W111" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="112" ht="13.55" customHeight="1" s="24">
       <c r="A112" s="9" t="n">
@@ -9524,9 +9196,6 @@
       <c r="V112" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W112" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="113" ht="13.55" customHeight="1" s="24">
       <c r="A113" s="9" t="n">
@@ -9597,9 +9266,6 @@
       <c r="V113" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W113" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="114" ht="13.55" customHeight="1" s="24">
       <c r="A114" s="9" t="n">
@@ -9670,9 +9336,6 @@
       <c r="V114" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W114" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="115" ht="13.55" customHeight="1" s="24">
       <c r="A115" s="9" t="n">
@@ -9743,9 +9406,6 @@
       <c r="V115" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W115" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="116" ht="13.55" customHeight="1" s="24">
       <c r="A116" s="9" t="n">
@@ -9816,9 +9476,6 @@
       <c r="V116" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W116" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="117" ht="13.55" customHeight="1" s="24">
       <c r="A117" s="9" t="n">
@@ -9889,9 +9546,6 @@
       <c r="V117" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W117" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="118" ht="13.55" customHeight="1" s="24">
       <c r="A118" s="9" t="n">
@@ -9962,9 +9616,6 @@
       <c r="V118" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W118" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="119" ht="13.55" customHeight="1" s="24">
       <c r="A119" s="9" t="n">
@@ -10035,9 +9686,6 @@
       <c r="V119" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W119" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="120" ht="13.55" customHeight="1" s="24">
       <c r="A120" s="9" t="n">
@@ -10108,9 +9756,6 @@
       <c r="V120" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W120" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="121" ht="13.55" customHeight="1" s="24">
       <c r="A121" s="9" t="n">
@@ -10181,9 +9826,6 @@
       <c r="V121" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W121" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="122" ht="13.55" customHeight="1" s="24">
       <c r="A122" s="9" t="n">
@@ -10254,9 +9896,6 @@
       <c r="V122" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W122" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="123" ht="13.55" customHeight="1" s="24">
       <c r="A123" s="9" t="n">
@@ -10327,9 +9966,6 @@
       <c r="V123" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W123" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="124" ht="13.55" customHeight="1" s="24">
       <c r="A124" s="9" t="n">
@@ -10400,9 +10036,6 @@
       <c r="V124" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W124" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="125" ht="13.55" customHeight="1" s="24">
       <c r="A125" s="9" t="n">
@@ -10473,9 +10106,6 @@
       <c r="V125" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W125" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="126" ht="13.55" customHeight="1" s="24">
       <c r="A126" s="9" t="n">
@@ -10546,9 +10176,6 @@
       <c r="V126" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W126" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="127" ht="13.55" customHeight="1" s="24">
       <c r="A127" s="9" t="n">
@@ -10619,9 +10246,6 @@
       <c r="V127" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W127" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="128" ht="13.55" customHeight="1" s="24">
       <c r="A128" s="9" t="n">
@@ -10692,9 +10316,6 @@
       <c r="V128" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W128" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="129" ht="13.55" customHeight="1" s="24">
       <c r="A129" s="9" t="n">
@@ -10765,9 +10386,6 @@
       <c r="V129" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W129" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="130" ht="13.55" customHeight="1" s="24">
       <c r="A130" s="9" t="n">
@@ -10838,9 +10456,6 @@
       <c r="V130" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W130" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="131" ht="13.55" customHeight="1" s="24">
       <c r="A131" s="9" t="n">
@@ -10911,9 +10526,6 @@
       <c r="V131" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W131" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="132" ht="13.55" customHeight="1" s="24">
       <c r="A132" s="9" t="n">
@@ -10984,9 +10596,6 @@
       <c r="V132" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W132" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="133" ht="13.55" customHeight="1" s="24">
       <c r="A133" s="9" t="n">
@@ -11057,9 +10666,6 @@
       <c r="V133" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W133" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="134" ht="13.55" customHeight="1" s="24">
       <c r="A134" s="9" t="n">
@@ -11130,9 +10736,6 @@
       <c r="V134" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W134" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="135" ht="13.55" customHeight="1" s="24">
       <c r="A135" s="9" t="n">
@@ -11203,9 +10806,6 @@
       <c r="V135" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W135" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="136" ht="13.55" customHeight="1" s="24">
       <c r="A136" s="9" t="n">
@@ -11276,9 +10876,6 @@
       <c r="V136" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W136" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="137" ht="13.55" customHeight="1" s="24">
       <c r="A137" s="9" t="n">
@@ -11349,9 +10946,6 @@
       <c r="V137" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W137" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="138" ht="13.55" customHeight="1" s="24">
       <c r="A138" s="9" t="n">
@@ -11422,9 +11016,6 @@
       <c r="V138" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W138" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="139" ht="13.55" customHeight="1" s="24">
       <c r="A139" s="9" t="n">
@@ -11495,9 +11086,6 @@
       <c r="V139" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W139" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="140" ht="13.55" customHeight="1" s="24">
       <c r="A140" s="9" t="n">
@@ -11568,9 +11156,6 @@
       <c r="V140" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W140" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="141" ht="13.55" customHeight="1" s="24">
       <c r="A141" s="9" t="n">
@@ -11641,9 +11226,6 @@
       <c r="V141" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W141" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="142" ht="13.55" customHeight="1" s="24">
       <c r="A142" s="9" t="n">
@@ -11714,9 +11296,6 @@
       <c r="V142" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W142" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="143" ht="13.55" customHeight="1" s="24">
       <c r="A143" s="9" t="n">
@@ -11787,9 +11366,6 @@
       <c r="V143" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W143" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="144" ht="13.55" customHeight="1" s="24">
       <c r="A144" s="9" t="n">
@@ -11860,9 +11436,6 @@
       <c r="V144" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W144" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="145" ht="13.55" customHeight="1" s="24">
       <c r="A145" s="9" t="n">
@@ -11933,9 +11506,6 @@
       <c r="V145" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W145" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="146" ht="13.55" customHeight="1" s="24">
       <c r="A146" s="9" t="n">
@@ -12006,9 +11576,6 @@
       <c r="V146" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W146" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="147" ht="13.55" customHeight="1" s="24">
       <c r="A147" s="9" t="n">
@@ -12079,9 +11646,6 @@
       <c r="V147" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W147" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="148" ht="13.55" customHeight="1" s="24">
       <c r="A148" s="9" t="n">
@@ -12152,9 +11716,6 @@
       <c r="V148" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W148" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="149" ht="13.55" customHeight="1" s="24">
       <c r="A149" s="9" t="n">
@@ -12225,9 +11786,6 @@
       <c r="V149" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W149" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="150" ht="13.55" customHeight="1" s="24">
       <c r="A150" s="9" t="n">
@@ -12298,9 +11856,6 @@
       <c r="V150" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W150" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="151" ht="13.55" customHeight="1" s="24">
       <c r="A151" s="9" t="n">
@@ -12371,9 +11926,6 @@
       <c r="V151" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W151" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="152" ht="13.55" customHeight="1" s="24">
       <c r="A152" s="9" t="n">
@@ -12444,9 +11996,6 @@
       <c r="V152" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W152" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="153" ht="13.55" customHeight="1" s="24">
       <c r="A153" s="9" t="n">
@@ -12517,9 +12066,6 @@
       <c r="V153" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W153" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="154" ht="13.55" customHeight="1" s="24">
       <c r="A154" s="9" t="n">
@@ -12590,9 +12136,6 @@
       <c r="V154" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W154" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="155" ht="13.55" customHeight="1" s="24">
       <c r="A155" s="9" t="n">
@@ -12663,9 +12206,6 @@
       <c r="V155" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W155" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="156" ht="13.55" customHeight="1" s="24">
       <c r="A156" s="9" t="n">
@@ -12736,9 +12276,6 @@
       <c r="V156" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W156" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="157" ht="13.55" customHeight="1" s="24">
       <c r="A157" s="9" t="n">
@@ -12809,9 +12346,6 @@
       <c r="V157" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W157" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="158" ht="13.55" customHeight="1" s="24">
       <c r="A158" s="9" t="n">
@@ -12882,9 +12416,6 @@
       <c r="V158" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W158" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="159" ht="13.55" customHeight="1" s="24">
       <c r="A159" s="9" t="n">
@@ -12955,9 +12486,6 @@
       <c r="V159" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W159" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="160" ht="13.55" customHeight="1" s="24">
       <c r="A160" s="9" t="n">
@@ -13028,9 +12556,6 @@
       <c r="V160" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W160" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="161" ht="13.55" customHeight="1" s="24">
       <c r="A161" s="9" t="n">
@@ -13101,9 +12626,6 @@
       <c r="V161" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W161" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="162" ht="13.55" customHeight="1" s="24">
       <c r="A162" s="9" t="n">
@@ -13174,9 +12696,6 @@
       <c r="V162" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W162" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="163" ht="13.55" customHeight="1" s="24">
       <c r="A163" s="9" t="n">
@@ -13247,9 +12766,6 @@
       <c r="V163" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W163" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="164" ht="13.55" customHeight="1" s="24">
       <c r="A164" s="9" t="n">
@@ -13320,9 +12836,6 @@
       <c r="V164" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W164" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="165" ht="13.55" customHeight="1" s="24">
       <c r="A165" s="9" t="n">
@@ -13393,9 +12906,6 @@
       <c r="V165" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W165" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="166" ht="13.55" customHeight="1" s="24">
       <c r="A166" s="9" t="n">
@@ -13466,9 +12976,6 @@
       <c r="V166" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W166" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="167" ht="13.55" customHeight="1" s="24">
       <c r="A167" s="9" t="n">
@@ -13539,9 +13046,6 @@
       <c r="V167" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W167" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="168" ht="13.55" customHeight="1" s="24">
       <c r="A168" s="9" t="n">
@@ -13612,9 +13116,6 @@
       <c r="V168" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W168" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="169" ht="13.55" customHeight="1" s="24">
       <c r="A169" s="9" t="n">
@@ -13685,9 +13186,6 @@
       <c r="V169" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W169" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="170" ht="13.55" customHeight="1" s="24">
       <c r="A170" s="9" t="n">
@@ -13758,9 +13256,6 @@
       <c r="V170" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W170" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="171" ht="13.55" customHeight="1" s="24">
       <c r="A171" s="9" t="n">
@@ -13831,9 +13326,6 @@
       <c r="V171" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W171" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="172" ht="13.55" customHeight="1" s="24">
       <c r="A172" s="9" t="n">
@@ -13904,9 +13396,6 @@
       <c r="V172" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W172" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="173" ht="13.55" customHeight="1" s="24">
       <c r="A173" s="9" t="n">
@@ -13977,9 +13466,6 @@
       <c r="V173" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W173" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="174" ht="13.55" customHeight="1" s="24">
       <c r="A174" s="9" t="n">
@@ -14050,9 +13536,6 @@
       <c r="V174" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W174" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="175" ht="13.55" customHeight="1" s="24">
       <c r="A175" s="9" t="n">
@@ -14123,9 +13606,6 @@
       <c r="V175" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W175" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="176" ht="13.55" customHeight="1" s="24">
       <c r="A176" s="9" t="n">
@@ -14196,9 +13676,6 @@
       <c r="V176" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W176" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="177" ht="13.55" customHeight="1" s="24">
       <c r="A177" s="9" t="n">
@@ -14269,9 +13746,6 @@
       <c r="V177" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W177" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="178" ht="13.55" customHeight="1" s="24">
       <c r="A178" s="9" t="n">
@@ -14342,9 +13816,6 @@
       <c r="V178" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W178" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="179" ht="13.55" customHeight="1" s="24">
       <c r="A179" s="9" t="n">
@@ -14415,9 +13886,6 @@
       <c r="V179" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W179" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="180" ht="13.55" customHeight="1" s="24">
       <c r="A180" s="9" t="n">
@@ -14488,9 +13956,6 @@
       <c r="V180" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W180" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="181" ht="13.55" customHeight="1" s="24">
       <c r="A181" s="9" t="n">
@@ -14561,9 +14026,6 @@
       <c r="V181" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W181" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="182" ht="13.55" customHeight="1" s="24">
       <c r="A182" s="9" t="n">
@@ -14634,9 +14096,6 @@
       <c r="V182" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W182" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="183" ht="13.55" customHeight="1" s="24">
       <c r="A183" s="9" t="n">
@@ -14707,9 +14166,6 @@
       <c r="V183" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W183" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="184" ht="13.55" customHeight="1" s="24">
       <c r="A184" s="9" t="n">
@@ -14780,9 +14236,6 @@
       <c r="V184" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W184" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="185" ht="13.55" customHeight="1" s="24">
       <c r="A185" s="9" t="n">
@@ -14853,9 +14306,6 @@
       <c r="V185" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W185" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="186" ht="13.55" customHeight="1" s="24">
       <c r="A186" s="9" t="n">
@@ -14926,9 +14376,6 @@
       <c r="V186" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W186" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="187" ht="13.55" customHeight="1" s="24">
       <c r="A187" s="9" t="n">
@@ -14999,9 +14446,6 @@
       <c r="V187" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W187" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="188" ht="13.55" customHeight="1" s="24">
       <c r="A188" s="9" t="n">
@@ -15072,9 +14516,6 @@
       <c r="V188" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W188" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="189" ht="13.55" customHeight="1" s="24">
       <c r="A189" s="9" t="n">
@@ -15145,9 +14586,6 @@
       <c r="V189" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W189" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="190" ht="13.55" customHeight="1" s="24">
       <c r="A190" s="9" t="n">
@@ -15218,9 +14656,6 @@
       <c r="V190" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W190" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="191" ht="13.55" customHeight="1" s="24">
       <c r="A191" s="9" t="n">
@@ -15291,9 +14726,6 @@
       <c r="V191" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W191" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="192" ht="13.55" customHeight="1" s="24">
       <c r="A192" s="9" t="n">
@@ -15364,9 +14796,6 @@
       <c r="V192" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W192" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="193" ht="13.55" customHeight="1" s="24">
       <c r="A193" s="9" t="n">
@@ -15437,9 +14866,6 @@
       <c r="V193" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W193" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="194" ht="13.55" customHeight="1" s="24">
       <c r="A194" s="9" t="n">
@@ -15510,9 +14936,6 @@
       <c r="V194" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W194" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="195" ht="13.55" customHeight="1" s="24">
       <c r="A195" s="9" t="n">
@@ -15583,9 +15006,6 @@
       <c r="V195" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W195" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="196" ht="13.55" customHeight="1" s="24">
       <c r="A196" s="9" t="n">
@@ -15656,9 +15076,6 @@
       <c r="V196" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W196" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="197" ht="13.55" customHeight="1" s="24">
       <c r="A197" s="9" t="n">
@@ -15729,9 +15146,6 @@
       <c r="V197" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W197" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="198" ht="13.55" customHeight="1" s="24">
       <c r="A198" s="9" t="n">
@@ -15802,9 +15216,6 @@
       <c r="V198" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W198" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="199" ht="13.55" customHeight="1" s="24">
       <c r="A199" s="9" t="n">
@@ -15875,9 +15286,6 @@
       <c r="V199" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W199" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="200" ht="13.55" customHeight="1" s="24">
       <c r="A200" s="9" t="n">
@@ -15948,9 +15356,6 @@
       <c r="V200" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W200" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="201" ht="13.55" customHeight="1" s="24">
       <c r="A201" s="9" t="n">
@@ -16021,9 +15426,6 @@
       <c r="V201" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W201" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="202" ht="13.55" customHeight="1" s="24">
       <c r="A202" s="9" t="n">
@@ -16094,9 +15496,6 @@
       <c r="V202" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W202" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="203" ht="13.55" customHeight="1" s="24">
       <c r="A203" s="9" t="n">
@@ -16167,9 +15566,6 @@
       <c r="V203" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W203" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="204" ht="13.55" customHeight="1" s="24">
       <c r="A204" s="9" t="n">
@@ -16240,9 +15636,6 @@
       <c r="V204" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W204" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="205" ht="13.55" customHeight="1" s="24">
       <c r="A205" s="9" t="n">
@@ -16313,9 +15706,6 @@
       <c r="V205" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W205" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="206" ht="13.55" customHeight="1" s="24">
       <c r="A206" s="9" t="n">
@@ -16386,9 +15776,6 @@
       <c r="V206" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W206" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="207" ht="13.55" customHeight="1" s="24">
       <c r="A207" s="9" t="n">
@@ -16459,9 +15846,6 @@
       <c r="V207" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W207" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="208" ht="13.55" customHeight="1" s="24">
       <c r="A208" s="9" t="n">
@@ -16532,9 +15916,6 @@
       <c r="V208" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W208" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="209" ht="13.55" customHeight="1" s="24">
       <c r="A209" s="9" t="n">
@@ -16605,9 +15986,6 @@
       <c r="V209" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W209" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="210" ht="13.55" customHeight="1" s="24">
       <c r="A210" s="9" t="n">
@@ -16678,9 +16056,6 @@
       <c r="V210" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W210" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="211" ht="13.55" customHeight="1" s="24">
       <c r="A211" s="9" t="n">
@@ -16751,9 +16126,6 @@
       <c r="V211" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W211" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="212" ht="13.55" customHeight="1" s="24">
       <c r="A212" s="9" t="n">
@@ -16824,9 +16196,6 @@
       <c r="V212" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W212" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="213" ht="26.55" customHeight="1" s="24">
       <c r="A213" s="9" t="n">
@@ -16898,9 +16267,6 @@
       <c r="V213" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W213" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="214" ht="13.55" customHeight="1" s="24">
       <c r="A214" s="9" t="n">
@@ -16971,9 +16337,6 @@
       <c r="V214" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W214" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="215" ht="13.55" customHeight="1" s="24">
       <c r="A215" s="9" t="n">
@@ -17044,9 +16407,6 @@
       <c r="V215" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W215" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="216" ht="13.55" customHeight="1" s="24">
       <c r="A216" s="9" t="n">
@@ -17117,9 +16477,6 @@
       <c r="V216" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W216" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="217" ht="13.55" customHeight="1" s="24">
       <c r="A217" s="9" t="n">
@@ -17190,9 +16547,6 @@
       <c r="V217" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W217" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="218" ht="13.55" customHeight="1" s="24">
       <c r="A218" s="9" t="n">
@@ -17263,9 +16617,6 @@
       <c r="V218" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W218" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="219" ht="13.55" customHeight="1" s="24">
       <c r="A219" s="9" t="n">
@@ -17336,9 +16687,6 @@
       <c r="V219" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W219" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="220" ht="13.55" customHeight="1" s="24">
       <c r="A220" s="9" t="n">
@@ -17409,9 +16757,6 @@
       <c r="V220" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W220" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="221" ht="13.55" customHeight="1" s="24">
       <c r="A221" s="9" t="n">
@@ -17482,9 +16827,6 @@
       <c r="V221" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W221" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="222" ht="13.55" customHeight="1" s="24">
       <c r="A222" s="9" t="n">
@@ -17555,9 +16897,6 @@
       <c r="V222" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W222" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="223" ht="13.55" customHeight="1" s="24">
       <c r="A223" s="9" t="n">
@@ -17628,9 +16967,6 @@
       <c r="V223" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W223" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="224" ht="13.55" customHeight="1" s="24">
       <c r="A224" s="9" t="n">
@@ -17701,9 +17037,6 @@
       <c r="V224" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W224" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="225" ht="13.55" customHeight="1" s="24">
       <c r="A225" s="9" t="n">
@@ -17774,9 +17107,6 @@
       <c r="V225" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W225" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="226" ht="13.55" customHeight="1" s="24">
       <c r="A226" s="9" t="n">
@@ -17847,9 +17177,6 @@
       <c r="V226" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W226" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="227" ht="13.55" customHeight="1" s="24">
       <c r="A227" s="9" t="n">
@@ -17920,9 +17247,6 @@
       <c r="V227" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W227" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="228" ht="14.05" customHeight="1" s="24">
       <c r="A228" s="12" t="n">
@@ -17993,9 +17317,6 @@
       <c r="V228" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="W228" s="9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="229" ht="14.15" customHeight="1" s="24">
       <c r="A229" s="14" t="inlineStr">
@@ -18064,9 +17385,6 @@
       <c r="V229" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="W229" s="16" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="230" ht="13.65" customHeight="1" s="24">
       <c r="A230" s="17" t="inlineStr">
@@ -18135,9 +17453,6 @@
       <c r="V230" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="W230" s="16" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="231" ht="13.65" customHeight="1" s="24">
       <c r="A231" s="19" t="inlineStr">
@@ -18203,10 +17518,7 @@
       <c r="U231" s="22" t="n">
         <v>136665</v>
       </c>
-      <c r="V231" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="W231" s="23" t="n">
+      <c r="V231" s="23" t="n">
         <v>0</v>
       </c>
     </row>
